--- a/artfynd/A 23935-2025 artfynd.xlsx
+++ b/artfynd/A 23935-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135017094</v>
+        <v>137568675</v>
       </c>
       <c r="B2" t="n">
-        <v>79104</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614412</v>
+        <v>613939</v>
       </c>
       <c r="R2" t="n">
-        <v>7256633</v>
+        <v>7256807</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,36 +771,35 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Gammal tallskog med inslag av senvuxna granar på myrholme</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017094</t>
+          <t>https://artportalen.se/Sighting/137568675</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135017091</v>
+        <v>135017094</v>
       </c>
       <c r="B3" t="n">
-        <v>83289</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614205</v>
+        <v>614412</v>
       </c>
       <c r="R3" t="n">
-        <v>7256772</v>
+        <v>7256633</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +880,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Lövrik, äldre barrblandskog på frisk mark på myrholme</t>
+          <t>Gammal tallskog med inslag av senvuxna granar på myrholme</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -888,16 +897,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017091</t>
+          <t>https://artportalen.se/Sighting/135017094</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135017100</v>
+        <v>137568652</v>
       </c>
       <c r="B4" t="n">
-        <v>91066</v>
+        <v>79205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,37 +914,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614401</v>
+        <v>614167</v>
       </c>
       <c r="R4" t="n">
-        <v>7256653</v>
+        <v>7256605</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,12 +968,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,71 +994,73 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Gammal tallskog med inslag av senvuxna granar på myrholme</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017100</t>
+          <t>https://artportalen.se/Sighting/137568652</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135017098</v>
+        <v>137568687</v>
       </c>
       <c r="B5" t="n">
-        <v>79438</v>
+        <v>79205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614222</v>
+        <v>614196</v>
       </c>
       <c r="R5" t="n">
-        <v>7256803</v>
+        <v>7256920</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,12 +1087,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,38 +1111,38 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Lövrik, äldre barrblandskog på frisk mark på myrholme</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017098</t>
+          <t>https://artportalen.se/Sighting/137568687</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135017101</v>
+        <v>137568679</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>92460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,37 +1150,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614229</v>
+        <v>614016</v>
       </c>
       <c r="R6" t="n">
-        <v>7256599</v>
+        <v>7256805</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1204,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,36 +1230,35 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Lövrik, äldre barrblandskog på frisk/torr mark på myrholme</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017101</t>
+          <t>https://artportalen.se/Sighting/137568679</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135017105</v>
+        <v>137568677</v>
       </c>
       <c r="B7" t="n">
-        <v>78841</v>
+        <v>92189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,37 +1266,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>614405</v>
+        <v>614010</v>
       </c>
       <c r="R7" t="n">
-        <v>7256826</v>
+        <v>7256835</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,12 +1323,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,38 +1347,38 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Lågproduktiv, lövrik äldre tallskog på blåbärsris med inslag av senvuxna granar</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017105</t>
+          <t>https://artportalen.se/Sighting/137568677</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135017096</v>
+        <v>137568678</v>
       </c>
       <c r="B8" t="n">
-        <v>83425</v>
+        <v>92189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,37 +1386,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>614217</v>
+        <v>614015</v>
       </c>
       <c r="R8" t="n">
-        <v>7256804</v>
+        <v>7256807</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,12 +1440,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,36 +1466,35 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Lövrik, äldre barrblandskog på frisk mark på myrholme</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017096</t>
+          <t>https://artportalen.se/Sighting/137568678</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135017086</v>
+        <v>137568680</v>
       </c>
       <c r="B9" t="n">
-        <v>80057</v>
+        <v>92189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,37 +1502,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>614188</v>
+        <v>614017</v>
       </c>
       <c r="R9" t="n">
-        <v>7256826</v>
+        <v>7256774</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,12 +1556,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,36 +1582,35 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Frisk, äldre barrblandskog på myrholme</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017086</t>
+          <t>https://artportalen.se/Sighting/137568680</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135017089</v>
+        <v>135017091</v>
       </c>
       <c r="B10" t="n">
-        <v>80057</v>
+        <v>83289</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1618,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>614400</v>
+        <v>614205</v>
       </c>
       <c r="R10" t="n">
-        <v>7256654</v>
+        <v>7256772</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1691,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Gammal tallskog med inslag av senvuxna granar på myrholme</t>
+          <t>Lövrik, äldre barrblandskog på frisk mark på myrholme</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1637,16 +1708,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017089</t>
+          <t>https://artportalen.se/Sighting/135017091</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135017102</v>
+        <v>135017100</v>
       </c>
       <c r="B11" t="n">
-        <v>78442</v>
+        <v>91066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,21 +1725,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>614405</v>
+        <v>614401</v>
       </c>
       <c r="R11" t="n">
-        <v>7256826</v>
+        <v>7256653</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1798,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Lågproduktiv, lövrik äldre tallskog på blåbärsris med inslag av senvuxna granar</t>
+          <t>Gammal tallskog med inslag av senvuxna granar på myrholme</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1744,16 +1815,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017102</t>
+          <t>https://artportalen.se/Sighting/135017100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135017097</v>
+        <v>137568648</v>
       </c>
       <c r="B12" t="n">
-        <v>80028</v>
+        <v>92111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,37 +1832,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>3242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>614188</v>
+        <v>614363</v>
       </c>
       <c r="R12" t="n">
-        <v>7256826</v>
+        <v>7256752</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,12 +1886,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,58 +1912,57 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Frisk, äldre barrblandskog på myrholme</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017097</t>
+          <t>https://artportalen.se/Sighting/137568648</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135017088</v>
+        <v>135017098</v>
       </c>
       <c r="B13" t="n">
-        <v>79461</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>614381</v>
+        <v>614222</v>
       </c>
       <c r="R13" t="n">
-        <v>7256707</v>
+        <v>7256803</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +2021,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gammal tallskog med inslag av senvuxna granar på myrholme</t>
+          <t>Lövrik, äldre barrblandskog på frisk mark på myrholme</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1958,16 +2038,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017088</t>
+          <t>https://artportalen.se/Sighting/135017098</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135017104</v>
+        <v>135017101</v>
       </c>
       <c r="B14" t="n">
-        <v>79461</v>
+        <v>78841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,21 +2055,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>260591</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>614348</v>
+        <v>614229</v>
       </c>
       <c r="R14" t="n">
-        <v>7256885</v>
+        <v>7256599</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,7 +2128,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Gammal tallskog med inslag av senvuxna granar på myrholme</t>
+          <t>Lövrik, äldre barrblandskog på frisk/torr mark på myrholme</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2065,7 +2145,1701 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135017101</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135017105</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>614405</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7256826</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Lågproduktiv, lövrik äldre tallskog på blåbärsris med inslag av senvuxna granar</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017105</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135017096</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83425</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>614217</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7256804</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Lövrik, äldre barrblandskog på frisk mark på myrholme</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017096</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135017086</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80057</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>614188</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7256826</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Frisk, äldre barrblandskog på myrholme</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017086</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135017089</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80057</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>614400</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7256654</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal tallskog med inslag av senvuxna granar på myrholme</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017089</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137568646</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80158</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>614381</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7256818</v>
+      </c>
+      <c r="S19" t="n">
+        <v>49</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568646</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137568674</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80158</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>613952</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7256781</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568674</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135017102</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78442</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>614405</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7256826</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Lågproduktiv, lövrik äldre tallskog på blåbärsris med inslag av senvuxna granar</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017102</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137568676</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>614017</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7256829</v>
+      </c>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Tydliga gamla ringhack.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568676</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137568681</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>614012</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7256774</v>
+      </c>
+      <c r="S23" t="n">
+        <v>40</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Skalad relativt klen gran.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568681</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137568682</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57224</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>613996</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7256771</v>
+      </c>
+      <c r="S24" t="n">
+        <v>19</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568682</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137568689</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58142</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>614371</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7256870</v>
+      </c>
+      <c r="S25" t="n">
+        <v>22</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568689</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135017097</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80028</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>614188</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7256826</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Frisk, äldre barrblandskog på myrholme</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017097</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135017088</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79461</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>614381</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7256707</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Gammal tallskog med inslag av senvuxna granar på myrholme</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017088</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135017104</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79461</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>614348</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7256885</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Gammal tallskog med inslag av senvuxna granar på myrholme</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135017104</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137568650</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79562</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>614391</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7256713</v>
+      </c>
+      <c r="S29" t="n">
+        <v>12</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568650</t>
         </is>
       </c>
     </row>
@@ -2084,6 +3858,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
